--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.5371443844063</v>
+        <v>6.912285962466025</v>
       </c>
       <c r="D2" t="n">
-        <v>45.26329449678052</v>
+        <v>7.355285355726836</v>
       </c>
       <c r="E2" t="n">
-        <v>13.39383976841008</v>
+        <v>2.176498962366639</v>
       </c>
       <c r="F2" t="n">
-        <v>11.88275562210422</v>
+        <v>1.930947788591935</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.53993620398445</v>
+        <v>2.037739633147474</v>
       </c>
       <c r="D3" t="n">
-        <v>24.19086855600893</v>
+        <v>3.931016140351452</v>
       </c>
       <c r="E3" t="n">
-        <v>13.39383976841008</v>
+        <v>2.176498962366639</v>
       </c>
       <c r="F3" t="n">
-        <v>11.88275562210422</v>
+        <v>1.930947788591935</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.99252463868206</v>
+        <v>5.848785253785834</v>
       </c>
       <c r="D4" t="n">
-        <v>36.07319338317442</v>
+        <v>5.861893924765844</v>
       </c>
       <c r="E4" t="n">
-        <v>13.39383976841008</v>
+        <v>2.176498962366639</v>
       </c>
       <c r="F4" t="n">
-        <v>11.88275562210422</v>
+        <v>1.930947788591935</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.62218770204843</v>
+        <v>4.48860550158287</v>
       </c>
       <c r="D5" t="n">
-        <v>25.56816363637481</v>
+        <v>4.154826590910907</v>
       </c>
       <c r="E5" t="n">
-        <v>13.39383976841008</v>
+        <v>2.176498962366639</v>
       </c>
       <c r="F5" t="n">
-        <v>11.88275562210422</v>
+        <v>1.930947788591935</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.8621735489746</v>
+        <v>7.940103201708373</v>
       </c>
       <c r="D6" t="n">
-        <v>50.45422829094009</v>
+        <v>8.198812097277765</v>
       </c>
       <c r="E6" t="n">
-        <v>13.39383976841008</v>
+        <v>2.176498962366639</v>
       </c>
       <c r="F6" t="n">
-        <v>11.88275562210422</v>
+        <v>1.930947788591935</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.53818586336897</v>
+        <v>7.237455202797459</v>
       </c>
       <c r="D7" t="n">
-        <v>49.98089963464221</v>
+        <v>8.121896190629359</v>
       </c>
       <c r="E7" t="n">
-        <v>13.39383976841008</v>
+        <v>2.176498962366639</v>
       </c>
       <c r="F7" t="n">
-        <v>11.88275562210422</v>
+        <v>1.930947788591935</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.74779061390754</v>
+        <v>9.059015974759976</v>
       </c>
       <c r="D8" t="n">
-        <v>56.98596853251748</v>
+        <v>9.26021988653409</v>
       </c>
       <c r="E8" t="n">
-        <v>13.39383976841008</v>
+        <v>2.176498962366639</v>
       </c>
       <c r="F8" t="n">
-        <v>11.88275562210422</v>
+        <v>1.930947788591935</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
